--- a/ACOES_SOCIAIS_modelo.xlsx
+++ b/ACOES_SOCIAIS_modelo.xlsx
@@ -1011,16 +1011,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>210</v>
+        <v>656</v>
       </c>
       <c r="C22" t="n">
-        <v>439</v>
+        <v>1015</v>
       </c>
       <c r="D22" t="n">
-        <v>361</v>
+        <v>1006</v>
       </c>
       <c r="E22" t="n">
-        <v>243</v>
+        <v>995</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1779</v>
+      </c>
+      <c r="H22" t="n">
+        <v>446</v>
+      </c>
+      <c r="J22" t="n">
+        <v>651</v>
+      </c>
+      <c r="K22" t="n">
+        <v>867</v>
       </c>
       <c r="L22">
         <f>SUM(B22:K22)</f>
@@ -1067,7 +1079,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C26" t="n">
         <v>99</v>
@@ -1307,6 +1319,21 @@
         <is>
           <t>037 - CULTURA</t>
         </is>
+      </c>
+      <c r="C36" t="n">
+        <v>300</v>
+      </c>
+      <c r="D36" t="n">
+        <v>500</v>
+      </c>
+      <c r="G36" t="n">
+        <v>800</v>
+      </c>
+      <c r="H36" t="n">
+        <v>500</v>
+      </c>
+      <c r="J36" t="n">
+        <v>400</v>
       </c>
       <c r="L36">
         <f>SUM(B36:K36)</f>
